--- a/output/pdf_financials_xlsx/KLE.H.xlsx
+++ b/output/pdf_financials_xlsx/KLE.H.xlsx
@@ -1380,7 +1380,7 @@
         <v>0.000255</v>
       </c>
       <c r="F15" s="3" t="n">
-        <v>0</v>
+        <v>0.029536</v>
       </c>
       <c r="G15" s="3" t="n">
         <v>0.0215</v>
@@ -1753,13 +1753,13 @@
         </is>
       </c>
       <c r="B22" s="3" t="n">
-        <v>1.62</v>
+        <v>-1.62</v>
       </c>
       <c r="C22" s="3" t="n">
         <v>-0.078</v>
       </c>
       <c r="D22" s="3" t="n">
-        <v>1.007</v>
+        <v>-1.007</v>
       </c>
       <c r="E22" s="3" t="n">
         <v>-0.520392</v>
@@ -2037,13 +2037,13 @@
         </is>
       </c>
       <c r="B26" s="3" t="n">
-        <v>1.62</v>
+        <v>-1.62</v>
       </c>
       <c r="C26" s="3" t="n">
         <v>-0.078</v>
       </c>
       <c r="D26" s="3" t="n">
-        <v>1.007</v>
+        <v>-1.007</v>
       </c>
       <c r="E26" s="3" t="n">
         <v>-0.520392</v>
@@ -2202,13 +2202,13 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>1.62</v>
+        <v>-1.62</v>
       </c>
       <c r="C29" s="3" t="n">
         <v>-0.078</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>1.007</v>
+        <v>-1.007</v>
       </c>
       <c r="E29" s="3" t="n">
         <v>-0.520392</v>
@@ -2514,13 +2514,13 @@
         </is>
       </c>
       <c r="B33" s="3" t="n">
-        <v>1.62</v>
+        <v>-1.62</v>
       </c>
       <c r="C33" s="3" t="n">
         <v>-0.078</v>
       </c>
       <c r="D33" s="3" t="n">
-        <v>1.007</v>
+        <v>-1.007</v>
       </c>
       <c r="E33" s="3" t="n">
         <v>-0.520392</v>
@@ -2578,25 +2578,25 @@
         <v>0</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.001099</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>0.023827</v>
       </c>
       <c r="G34" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>0.319862</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>0.202329</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>0.152581</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>0.026951</v>
       </c>
       <c r="L34" s="3" t="n">
         <v>0</v>
@@ -2624,34 +2624,34 @@
         </is>
       </c>
       <c r="B35" s="3" t="n">
-        <v>1.62</v>
+        <v>-1.62</v>
       </c>
       <c r="C35" s="3" t="n">
         <v>-0.078</v>
       </c>
       <c r="D35" s="3" t="n">
-        <v>1.007</v>
+        <v>-1.007</v>
       </c>
       <c r="E35" s="3" t="n">
-        <v>-0.520392</v>
+        <v>-0.519293</v>
       </c>
       <c r="F35" s="3" t="n">
-        <v>-0.201773</v>
+        <v>-0.177946</v>
       </c>
       <c r="G35" s="3" t="n">
         <v>-2.665438</v>
       </c>
       <c r="H35" s="3" t="n">
-        <v>-1.527237</v>
+        <v>-1.207375</v>
       </c>
       <c r="I35" s="3" t="n">
-        <v>-3.790493</v>
+        <v>-3.588164</v>
       </c>
       <c r="J35" s="3" t="n">
-        <v>-1.334016</v>
+        <v>-1.181435</v>
       </c>
       <c r="K35" s="3" t="n">
-        <v>0.138777</v>
+        <v>0.165728</v>
       </c>
       <c r="L35" s="3" t="n">
         <v>0.965766</v>
@@ -2679,31 +2679,31 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>16200</v>
+        <v>-16200</v>
       </c>
       <c r="C36" s="3" t="n">
         <v>-7800</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>100700</v>
+        <v>-100700</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>-2384.384879725086</v>
+        <v>-2379.349369988545</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>-52.17426156300665</v>
+        <v>-46.01309961239007</v>
       </c>
       <c r="G36" s="3" t="n">
         <v>-12397.38604651163</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>-929.7963532312563</v>
+        <v>-735.0613375544124</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>-1948.839588688946</v>
+        <v>-1844.814395886889</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>-2944.847682119205</v>
+        <v>-2608.024282560707</v>
       </c>
       <c r="K36" s="1" t="inlineStr">
         <is>
@@ -2746,13 +2746,13 @@
         </is>
       </c>
       <c r="B37" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="C37" s="3" t="n">
         <v>-0</v>
       </c>
       <c r="D37" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="E37" s="3" t="n">
         <v>-0</v>
@@ -2801,13 +2801,13 @@
         </is>
       </c>
       <c r="B38" s="3" t="n">
-        <v>16200</v>
+        <v>-16200</v>
       </c>
       <c r="C38" s="3" t="n">
         <v>-7800</v>
       </c>
       <c r="D38" s="3" t="n">
-        <v>100700</v>
+        <v>-100700</v>
       </c>
       <c r="E38" s="3" t="n">
         <v>-2384.384879725086</v>
@@ -8581,13 +8581,13 @@
         </is>
       </c>
       <c r="B114" s="3" t="n">
-        <v>1.62</v>
+        <v>-1.62</v>
       </c>
       <c r="C114" s="3" t="n">
         <v>-0.078</v>
       </c>
       <c r="D114" s="3" t="n">
-        <v>1.007</v>
+        <v>-1.007</v>
       </c>
       <c r="E114" s="3" t="n">
         <v>-0.520392</v>
@@ -46405,7 +46405,7 @@
       </c>
       <c r="D375" t="inlineStr">
         <is>
-          <t>Amortization</t>
+          <t>DepreciationAndAmortization</t>
         </is>
       </c>
       <c r="E375" t="inlineStr">
@@ -52247,7 +52247,11 @@
           <t>Royalty expenses</t>
         </is>
       </c>
-      <c r="D437" t="inlineStr"/>
+      <c r="D437" t="inlineStr">
+        <is>
+          <t>OtherOperatingExpenses</t>
+        </is>
+      </c>
       <c r="E437" t="inlineStr">
         <is>
           <t>-</t>
@@ -52269,7 +52273,7 @@
         </is>
       </c>
       <c r="I437" s="5" t="n">
-        <v>-0.029536</v>
+        <v>0.029536</v>
       </c>
       <c r="J437" t="inlineStr">
         <is>
@@ -55389,7 +55393,7 @@
         <v>-0.078</v>
       </c>
       <c r="G469" s="5" t="n">
-        <v>1.007</v>
+        <v>-1.007</v>
       </c>
       <c r="H469" t="inlineStr">
         <is>
@@ -55761,7 +55765,7 @@
         </is>
       </c>
       <c r="E473" s="5" t="n">
-        <v>1.62</v>
+        <v>-1.62</v>
       </c>
       <c r="F473" s="5" t="n">
         <v>-0.078</v>

--- a/output/pdf_financials_xlsx/KLE.H.xlsx
+++ b/output/pdf_financials_xlsx/KLE.H.xlsx
@@ -613,17 +613,25 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M4" s="3" t="n">
-        <v>0.000211</v>
-      </c>
-      <c r="N4" s="3" t="n">
-        <v>0.000105</v>
-      </c>
-      <c r="O4" s="3" t="n">
-        <v>0.001712</v>
-      </c>
-      <c r="P4" s="3" t="n">
-        <v>0.001958</v>
+      <c r="M4" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N4" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O4" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P4" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="Q4" s="1" t="inlineStr">
         <is>
@@ -1566,16 +1574,16 @@
         <v>0</v>
       </c>
       <c r="M18" s="3" t="n">
-        <v>0</v>
+        <v>0.000211</v>
       </c>
       <c r="N18" s="3" t="n">
-        <v>0</v>
+        <v>0.000105</v>
       </c>
       <c r="O18" s="3" t="n">
-        <v>0</v>
+        <v>0.001712</v>
       </c>
       <c r="P18" s="3" t="n">
-        <v>0</v>
+        <v>0.001958</v>
       </c>
       <c r="Q18" s="3" t="n">
         <v>0</v>
@@ -2547,16 +2555,16 @@
         <v>0.965766</v>
       </c>
       <c r="M33" s="3" t="n">
-        <v>-0.09246799999999999</v>
+        <v>-0.092679</v>
       </c>
       <c r="N33" s="3" t="n">
-        <v>0.241172</v>
+        <v>0.241067</v>
       </c>
       <c r="O33" s="3" t="n">
-        <v>-0.04668</v>
+        <v>-0.048392</v>
       </c>
       <c r="P33" s="3" t="n">
-        <v>-0.07048500000000001</v>
+        <v>-0.07244299999999999</v>
       </c>
       <c r="Q33" s="3" t="n">
         <v>-0.07048500000000001</v>
@@ -2657,16 +2665,16 @@
         <v>0.965766</v>
       </c>
       <c r="M35" s="3" t="n">
-        <v>-0.09246799999999999</v>
+        <v>-0.092679</v>
       </c>
       <c r="N35" s="3" t="n">
-        <v>0.241172</v>
+        <v>0.241067</v>
       </c>
       <c r="O35" s="3" t="n">
-        <v>-0.04668</v>
+        <v>-0.048392</v>
       </c>
       <c r="P35" s="3" t="n">
-        <v>-0.07048500000000001</v>
+        <v>-0.07244299999999999</v>
       </c>
       <c r="Q35" s="3" t="n">
         <v>-0.07048500000000001</v>
@@ -3368,25 +3376,17 @@
           <t xml:space="preserve">    Cash and Cash Equivalents</t>
         </is>
       </c>
-      <c r="B46" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C46" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D46" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E46" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B46" s="3" t="n">
+        <v>0.042</v>
+      </c>
+      <c r="C46" s="3" t="n">
+        <v>0.011</v>
+      </c>
+      <c r="D46" s="3" t="n">
+        <v>0.027</v>
+      </c>
+      <c r="E46" s="3" t="n">
+        <v>0.83482</v>
       </c>
       <c r="F46" s="3" t="n">
         <v>3.484672</v>
@@ -3518,25 +3518,17 @@
           <t xml:space="preserve">  Cash, Cash Equivalents, Marketable Securities</t>
         </is>
       </c>
-      <c r="B48" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C48" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D48" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E48" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B48" s="3" t="n">
+        <v>0.042</v>
+      </c>
+      <c r="C48" s="3" t="n">
+        <v>0.011</v>
+      </c>
+      <c r="D48" s="3" t="n">
+        <v>0.027</v>
+      </c>
+      <c r="E48" s="3" t="n">
+        <v>0.83482</v>
       </c>
       <c r="F48" s="3" t="n">
         <v>3.484672</v>
@@ -4522,13 +4514,15 @@
         </is>
       </c>
       <c r="C60" s="3" t="n">
-        <v>0.011</v>
+        <v>0</v>
       </c>
       <c r="D60" s="3" t="n">
-        <v>1.380347</v>
-      </c>
-      <c r="E60" s="3" t="n">
-        <v>0.061909</v>
+        <v>1.353347</v>
+      </c>
+      <c r="E60" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F60" s="3" t="n">
         <v>0.117546</v>
@@ -22645,7 +22639,7 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
@@ -24595,7 +24589,7 @@
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E146" s="5" t="n">
@@ -42397,7 +42391,7 @@
       </c>
       <c r="D333" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E333" t="inlineStr">

--- a/output/pdf_financials_xlsx/KLE.H.xlsx
+++ b/output/pdf_financials_xlsx/KLE.H.xlsx
@@ -578,40 +578,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F4" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G4" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H4" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I4" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J4" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K4" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L4" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F4" s="3" t="n">
+        <v>0.00066</v>
+      </c>
+      <c r="G4" s="3" t="n">
+        <v>0.002302</v>
+      </c>
+      <c r="H4" s="3" t="n">
+        <v>0.007761</v>
+      </c>
+      <c r="I4" s="3" t="n">
+        <v>0.000402</v>
+      </c>
+      <c r="J4" s="3" t="n">
+        <v>0.000344</v>
+      </c>
+      <c r="K4" s="3" t="n">
+        <v>0.000484</v>
+      </c>
+      <c r="L4" s="3" t="n">
+        <v>0.000751</v>
       </c>
       <c r="M4" s="1" t="inlineStr">
         <is>
@@ -2045,13 +2031,13 @@
         </is>
       </c>
       <c r="B26" s="3" t="n">
-        <v>-1.62</v>
+        <v>-0.078</v>
       </c>
       <c r="C26" s="3" t="n">
         <v>-0.078</v>
       </c>
       <c r="D26" s="3" t="n">
-        <v>-1.007</v>
+        <v>-0.08</v>
       </c>
       <c r="E26" s="3" t="n">
         <v>-0.520392</v>
@@ -8575,13 +8561,13 @@
         </is>
       </c>
       <c r="B114" s="3" t="n">
-        <v>-1.62</v>
+        <v>1.62</v>
       </c>
       <c r="C114" s="3" t="n">
         <v>-0.078</v>
       </c>
       <c r="D114" s="3" t="n">
-        <v>-1.007</v>
+        <v>1.007</v>
       </c>
       <c r="E114" s="3" t="n">
         <v>-0.520392</v>
@@ -8960,13 +8946,13 @@
         </is>
       </c>
       <c r="B121" s="3" t="n">
-        <v>0</v>
+        <v>-1.669</v>
       </c>
       <c r="C121" s="3" t="n">
-        <v>0</v>
+        <v>-0.002</v>
       </c>
       <c r="D121" s="3" t="n">
-        <v>0</v>
+        <v>-0.9399999999999999</v>
       </c>
       <c r="E121" s="3" t="n">
         <v>-0.015945</v>
@@ -9930,7 +9916,7 @@
         <v>0</v>
       </c>
       <c r="K138" s="3" t="n">
-        <v>0</v>
+        <v>0.113331</v>
       </c>
       <c r="L138" s="3" t="n">
         <v>0</v>
@@ -10040,7 +10026,7 @@
         <v>0</v>
       </c>
       <c r="K140" s="3" t="n">
-        <v>0</v>
+        <v>0.113331</v>
       </c>
       <c r="L140" s="3" t="n">
         <v>0</v>
@@ -30199,7 +30185,11 @@
           <t>Increase in long term debt</t>
         </is>
       </c>
-      <c r="D205" t="inlineStr"/>
+      <c r="D205" t="inlineStr">
+        <is>
+          <t>IssuanceOfDebt</t>
+        </is>
+      </c>
       <c r="E205" t="inlineStr">
         <is>
           <t>-</t>
@@ -31547,7 +31537,11 @@
           <t>Increase in long term debt</t>
         </is>
       </c>
-      <c r="D219" t="inlineStr"/>
+      <c r="D219" t="inlineStr">
+        <is>
+          <t>IssuanceOfDebt</t>
+        </is>
+      </c>
       <c r="E219" t="inlineStr">
         <is>
           <t>-</t>
@@ -39963,7 +39957,11 @@
           <t>Net Income (loss) $</t>
         </is>
       </c>
-      <c r="D307" t="inlineStr"/>
+      <c r="D307" t="inlineStr">
+        <is>
+          <t>NetIncomeFromContinuingOperations</t>
+        </is>
+      </c>
       <c r="E307" s="5" t="n">
         <v>1.62</v>
       </c>
@@ -40055,7 +40053,11 @@
           <t>Net change in non-cash operating working capital</t>
         </is>
       </c>
-      <c r="D308" t="inlineStr"/>
+      <c r="D308" t="inlineStr">
+        <is>
+          <t>ChangeInWorkingCapital</t>
+        </is>
+      </c>
       <c r="E308" s="5" t="n">
         <v>-1.669</v>
       </c>
@@ -46659,7 +46661,11 @@
           <t>Interest revenue</t>
         </is>
       </c>
-      <c r="D378" t="inlineStr"/>
+      <c r="D378" t="inlineStr">
+        <is>
+          <t>InterestIncome</t>
+        </is>
+      </c>
       <c r="E378" t="inlineStr">
         <is>
           <t>-</t>
@@ -49021,7 +49027,11 @@
           <t>Interest revenue</t>
         </is>
       </c>
-      <c r="D403" t="inlineStr"/>
+      <c r="D403" t="inlineStr">
+        <is>
+          <t>InterestIncome</t>
+        </is>
+      </c>
       <c r="E403" t="inlineStr">
         <is>
           <t>-</t>
@@ -55183,7 +55193,11 @@
           <t>Profit (Loss) from continuing operations</t>
         </is>
       </c>
-      <c r="D467" t="inlineStr"/>
+      <c r="D467" t="inlineStr">
+        <is>
+          <t>NetIncomeContinuousOperations</t>
+        </is>
+      </c>
       <c r="E467" t="inlineStr">
         <is>
           <t>-</t>
@@ -55563,7 +55577,11 @@
           <t>Profit (loss) from continuing operations</t>
         </is>
       </c>
-      <c r="D471" t="inlineStr"/>
+      <c r="D471" t="inlineStr">
+        <is>
+          <t>NetIncomeContinuousOperations</t>
+        </is>
+      </c>
       <c r="E471" s="5" t="n">
         <v>-0.078</v>
       </c>
